--- a/xls/square_12_tri3_16.xlsx
+++ b/xls/square_12_tri3_16.xlsx
@@ -482,13 +482,13 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>-2.027569357015289</v>
+        <v>-2.0275671463514233</v>
       </c>
       <c r="J16">
-        <v>-1.7667029798922018</v>
+        <v>-1.7667028309262882</v>
       </c>
       <c r="K16">
-        <v>1.383659795508467</v>
+        <v>1.3836561505210851</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -517,13 +517,13 @@
         <v>1734</v>
       </c>
       <c r="I17">
-        <v>-1.8894608129509454</v>
+        <v>-1.8894609520214185</v>
       </c>
       <c r="J17">
-        <v>-1.490006505293229</v>
+        <v>-1.4900065789088257</v>
       </c>
       <c r="K17">
-        <v>3.058761007430406</v>
+        <v>3.058761050746253</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -552,13 +552,13 @@
         <v>1944</v>
       </c>
       <c r="I18">
-        <v>-0.8254754357809104</v>
+        <v>-0.8254754427196027</v>
       </c>
       <c r="J18">
-        <v>-0.6772428913023848</v>
+        <v>-0.6772428945060708</v>
       </c>
       <c r="K18">
-        <v>3.7911859034571687</v>
+        <v>3.7911859039806983</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -587,13 +587,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>-0.20380584998404763</v>
+        <v>-0.20380585122796263</v>
       </c>
       <c r="J19">
-        <v>-0.18402566699691755</v>
+        <v>-0.18402566824365957</v>
       </c>
       <c r="K19">
-        <v>3.9226007239508887</v>
+        <v>3.922600726787693</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -622,13 +622,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-0.0019150597766216075</v>
+        <v>-0.0019150597779125915</v>
       </c>
       <c r="J20">
-        <v>-0.0014013354715429864</v>
+        <v>-0.0014013354721588614</v>
       </c>
       <c r="K20">
-        <v>2.8978337025283136</v>
+        <v>2.8978337024557463</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -657,13 +657,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>-0.0004971986577513425</v>
+        <v>-0.0004971986568811984</v>
       </c>
       <c r="J21">
-        <v>-0.0004433255834785947</v>
+        <v>-0.000443325582977308</v>
       </c>
       <c r="K21">
-        <v>2.7364207989139984</v>
+        <v>2.7364207988760274</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -692,13 +692,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-0.0003677590188720068</v>
+        <v>-0.00036775901950514153</v>
       </c>
       <c r="J22">
-        <v>-0.0002478093558015499</v>
+        <v>-0.0002478093561569144</v>
       </c>
       <c r="K22">
-        <v>2.474984708363708</v>
+        <v>2.474984708753606</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -727,13 +727,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-0.0018555672219230887</v>
+        <v>-0.0018555672240561142</v>
       </c>
       <c r="J23">
-        <v>-0.0013266263190652421</v>
+        <v>-0.0013266263205815466</v>
       </c>
       <c r="K23">
-        <v>2.8593645183870477</v>
+        <v>2.8593645190682606</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -762,13 +762,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-8.532148962398042e-5</v>
+        <v>-8.532148964249915e-5</v>
       </c>
       <c r="J24">
-        <v>-6.267111593059649e-5</v>
+        <v>-6.26711159434239e-5</v>
       </c>
       <c r="K24">
-        <v>2.229250606227323</v>
+        <v>2.2292506060328012</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -797,13 +797,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>-5.702634541407633e-5</v>
+        <v>-5.702634540568558e-5</v>
       </c>
       <c r="J25">
-        <v>-3.550065127751414e-5</v>
+        <v>-3.550065127259567e-5</v>
       </c>
       <c r="K25">
-        <v>1.9951789327328644</v>
+        <v>1.9951789325901619</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -832,13 +832,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-4.6700114190638374e-5</v>
+        <v>-4.6700114190059714e-5</v>
       </c>
       <c r="J26">
-        <v>-3.709242504626298e-5</v>
+        <v>-3.7092425046166534e-5</v>
       </c>
       <c r="K26">
-        <v>2.1476381483890514</v>
+        <v>2.147638148417947</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -867,13 +867,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-3.6208579052232986e-7</v>
+        <v>-3.6208579081162836e-7</v>
       </c>
       <c r="J27">
-        <v>-2.66620347099149e-6</v>
+        <v>-2.6662034710879233e-6</v>
       </c>
       <c r="K27">
-        <v>1.83078190984735</v>
+        <v>1.830781910042145</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -902,13 +902,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-4.069444142438166e-5</v>
+        <v>-4.069444142688915e-5</v>
       </c>
       <c r="J28">
-        <v>-3.062539788402482e-5</v>
+        <v>-3.062539788571251e-5</v>
       </c>
       <c r="K28">
-        <v>2.080988083751685</v>
+        <v>2.080988083817837</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -940,10 +940,10 @@
         <v>-4.7430536587972424e-6</v>
       </c>
       <c r="J29">
-        <v>-3.5869214716528087e-6</v>
+        <v>-3.5869214715563753e-6</v>
       </c>
       <c r="K29">
-        <v>1.6525931457745953</v>
+        <v>1.6525931458155498</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -972,13 +972,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-1.5311179931035515e-5</v>
+        <v>-1.5311179931565913e-5</v>
       </c>
       <c r="J30">
-        <v>-1.2017735836295859e-5</v>
+        <v>-1.2017735836826254e-5</v>
       </c>
       <c r="K30">
-        <v>1.901251529146705</v>
+        <v>1.9012515292306729</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1010,10 +1010,10 @@
         <v>1.7906357600813668e-6</v>
       </c>
       <c r="J31">
-        <v>1.7324831115972938e-7</v>
+        <v>1.732483112561621e-7</v>
       </c>
       <c r="K31">
-        <v>1.5806760073858601</v>
+        <v>1.5806760075472006</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1042,13 +1042,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-2.9127946284247044e-5</v>
+        <v>-2.9127946285018555e-5</v>
       </c>
       <c r="J32">
-        <v>-1.8186875366978626e-5</v>
+        <v>-1.8186875367605467e-5</v>
       </c>
       <c r="K32">
-        <v>1.8241294715480496</v>
+        <v>1.8241294713407188</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_12_tri3_16.xlsx
+++ b/xls/square_12_tri3_16.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>289</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14">
+        <v>169</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14">
+        <v>225</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14">
+        <v>1176</v>
+      </c>
+      <c r="I14">
+        <v>2.9390169291553376</v>
+      </c>
+      <c r="J14">
+        <v>-0.30762627975564205</v>
+      </c>
+      <c r="K14">
+        <v>3.334089513980112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15">
+        <v>289</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15">
+        <v>169</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15">
+        <v>256</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15">
+        <v>1350</v>
+      </c>
+      <c r="I15">
+        <v>1.7800538383987554</v>
+      </c>
+      <c r="J15">
+        <v>-1.0944522103113283</v>
+      </c>
+      <c r="K15">
+        <v>2.87818591277585</v>
+      </c>
+    </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
         <v>11</v>
